--- a/document/成果物ドキュメント_ログアウト機能.xlsx
+++ b/document/成果物ドキュメント_ログアウト機能.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE58A6E-07AC-4D4E-AD00-658ACD30EB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1565A45-60DD-4B1C-AF7B-199D0054CFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -279,54 +279,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.ユーザーがメニュー画面を開く
-2.ユーザーがログアウトボタンを押下する
-3.システムがログイン情報が削除される
-4.ログアウト画面画面が表示される
-5.ユーザーがログイン画面戻るボタンを押下する
-6.システムがログイン画面を表示する</t>
-    <rPh sb="11" eb="13">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="89" eb="90">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="111" eb="113">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>POST</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -392,6 +344,54 @@
   </si>
   <si>
     <t>TaskManager62システム</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.ユーザーがメニュー画面を開く
+2.ユーザーがログアウトボタンを選択する
+3.システムがログイン情報を削除する
+4.システムがログアウト画面画面を表示する
+5.ユーザーがログイン画面へ戻るを選択する
+6.システムがログイン画面を表示する</t>
+    <rPh sb="11" eb="13">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒラ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="52" eb="54">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="71" eb="73">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="74" eb="76">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="90" eb="92">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="93" eb="94">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="96" eb="98">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="112" eb="114">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>ヒョウジ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1386,59 +1386,62 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1449,9 +1452,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1470,35 +1470,35 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2021,7 +2021,7 @@
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
       <c r="E8" s="69" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F8" s="50"/>
       <c r="G8" s="50"/>
@@ -3088,7 +3088,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="81" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="47"/>
@@ -3156,44 +3156,44 @@
       <c r="J4" s="45"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="78" t="s">
+      <c r="A5" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="79"/>
+      <c r="B5" s="74"/>
       <c r="C5" s="56"/>
-      <c r="D5" s="85" t="s">
+      <c r="D5" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="86"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="71" t="s">
+      <c r="A6" s="83" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="64"/>
       <c r="C6" s="65"/>
-      <c r="D6" s="72" t="s">
-        <v>84</v>
+      <c r="D6" s="76" t="s">
+        <v>83</v>
       </c>
       <c r="E6" s="64"/>
       <c r="F6" s="64"/>
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="I6" s="64"/>
-      <c r="J6" s="73"/>
+      <c r="J6" s="77"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="71" t="s">
+      <c r="A7" s="83" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="64"/>
       <c r="C7" s="65"/>
-      <c r="D7" s="72" t="s">
+      <c r="D7" s="76" t="s">
         <v>71</v>
       </c>
       <c r="E7" s="64"/>
@@ -3201,103 +3201,103 @@
       <c r="G7" s="64"/>
       <c r="H7" s="64"/>
       <c r="I7" s="64"/>
-      <c r="J7" s="73"/>
+      <c r="J7" s="77"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="83" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="64"/>
       <c r="C8" s="65"/>
-      <c r="D8" s="72" t="s">
-        <v>83</v>
+      <c r="D8" s="76" t="s">
+        <v>82</v>
       </c>
       <c r="E8" s="64"/>
       <c r="F8" s="64"/>
       <c r="G8" s="64"/>
       <c r="H8" s="64"/>
       <c r="I8" s="64"/>
-      <c r="J8" s="73"/>
+      <c r="J8" s="77"/>
     </row>
     <row r="9" spans="1:10" ht="91.5" customHeight="1">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="84" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="70" t="s">
+      <c r="B9" s="87" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="65"/>
-      <c r="D9" s="87" t="s">
-        <v>74</v>
+      <c r="D9" s="78" t="s">
+        <v>85</v>
       </c>
       <c r="E9" s="64"/>
       <c r="F9" s="64"/>
       <c r="G9" s="64"/>
       <c r="H9" s="64"/>
       <c r="I9" s="64"/>
-      <c r="J9" s="73"/>
+      <c r="J9" s="77"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="70" t="s">
+      <c r="A10" s="85"/>
+      <c r="B10" s="87" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="65"/>
-      <c r="D10" s="72" t="s">
-        <v>81</v>
+      <c r="D10" s="76" t="s">
+        <v>80</v>
       </c>
       <c r="E10" s="64"/>
       <c r="F10" s="64"/>
       <c r="G10" s="64"/>
       <c r="H10" s="64"/>
       <c r="I10" s="64"/>
-      <c r="J10" s="73"/>
+      <c r="J10" s="77"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="82"/>
-      <c r="B11" s="70" t="s">
+      <c r="A11" s="86"/>
+      <c r="B11" s="87" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="65"/>
-      <c r="D11" s="72" t="s">
-        <v>81</v>
+      <c r="D11" s="76" t="s">
+        <v>80</v>
       </c>
       <c r="E11" s="64"/>
       <c r="F11" s="64"/>
       <c r="G11" s="64"/>
       <c r="H11" s="64"/>
       <c r="I11" s="64"/>
-      <c r="J11" s="73"/>
+      <c r="J11" s="77"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="71" t="s">
+      <c r="A12" s="83" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="64"/>
       <c r="C12" s="65"/>
-      <c r="D12" s="72" t="s">
-        <v>82</v>
+      <c r="D12" s="76" t="s">
+        <v>81</v>
       </c>
       <c r="E12" s="64"/>
       <c r="F12" s="64"/>
       <c r="G12" s="64"/>
       <c r="H12" s="64"/>
       <c r="I12" s="64"/>
-      <c r="J12" s="73"/>
+      <c r="J12" s="77"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="75"/>
-      <c r="C13" s="76"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
-      <c r="J13" s="84"/>
+      <c r="B13" s="71"/>
+      <c r="C13" s="80"/>
+      <c r="D13" s="70"/>
+      <c r="E13" s="71"/>
+      <c r="F13" s="71"/>
+      <c r="G13" s="71"/>
+      <c r="H13" s="71"/>
+      <c r="I13" s="71"/>
+      <c r="J13" s="72"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4288,6 +4288,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4296,25 +4315,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -7237,23 +7237,23 @@
       <c r="J4" s="44"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="79"/>
+      <c r="B5" s="74"/>
       <c r="C5" s="56"/>
       <c r="D5" s="92" t="s">
         <v>73</v>
       </c>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="86"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="91" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="64"/>
@@ -7264,7 +7264,7 @@
       <c r="G6" s="64"/>
       <c r="H6" s="64"/>
       <c r="I6" s="64"/>
-      <c r="J6" s="73"/>
+      <c r="J6" s="77"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="93"/>
@@ -7351,7 +7351,7 @@
       <c r="J13" s="96"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="90" t="s">
+      <c r="A14" s="91" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="64"/>
@@ -7362,16 +7362,16 @@
       <c r="G14" s="64"/>
       <c r="H14" s="64"/>
       <c r="I14" s="64"/>
-      <c r="J14" s="73"/>
+      <c r="J14" s="77"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="91" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="64"/>
       <c r="C15" s="65"/>
-      <c r="D15" s="72" t="s">
-        <v>76</v>
+      <c r="D15" s="76" t="s">
+        <v>75</v>
       </c>
       <c r="E15" s="64"/>
       <c r="F15" s="64"/>
@@ -7381,11 +7381,11 @@
         <v>27</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="90" t="s">
+      <c r="A16" s="91" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="64"/>
@@ -7406,101 +7406,101 @@
         <v>19</v>
       </c>
       <c r="I16" s="64"/>
-      <c r="J16" s="73"/>
+      <c r="J16" s="77"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="91" t="s">
-        <v>77</v>
+      <c r="A17" s="88" t="s">
+        <v>76</v>
       </c>
       <c r="B17" s="64"/>
       <c r="C17" s="65"/>
       <c r="D17" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H17" s="76" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="72" t="s">
-        <v>80</v>
-      </c>
       <c r="I17" s="64"/>
-      <c r="J17" s="73"/>
+      <c r="J17" s="77"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="91"/>
+      <c r="A18" s="88"/>
       <c r="B18" s="64"/>
       <c r="C18" s="65"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="72"/>
+      <c r="H18" s="76"/>
       <c r="I18" s="64"/>
-      <c r="J18" s="73"/>
+      <c r="J18" s="77"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="91"/>
+      <c r="A19" s="88"/>
       <c r="B19" s="64"/>
       <c r="C19" s="65"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="72"/>
+      <c r="H19" s="76"/>
       <c r="I19" s="64"/>
-      <c r="J19" s="73"/>
+      <c r="J19" s="77"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="91"/>
+      <c r="A20" s="88"/>
       <c r="B20" s="64"/>
       <c r="C20" s="65"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="72"/>
+      <c r="H20" s="76"/>
       <c r="I20" s="64"/>
-      <c r="J20" s="73"/>
+      <c r="J20" s="77"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="91"/>
+      <c r="A21" s="88"/>
       <c r="B21" s="64"/>
       <c r="C21" s="65"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="72"/>
+      <c r="H21" s="76"/>
       <c r="I21" s="64"/>
-      <c r="J21" s="73"/>
+      <c r="J21" s="77"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="91"/>
+      <c r="A22" s="88"/>
       <c r="B22" s="64"/>
       <c r="C22" s="65"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="72"/>
+      <c r="H22" s="76"/>
       <c r="I22" s="64"/>
-      <c r="J22" s="73"/>
+      <c r="J22" s="77"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="89"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="76"/>
+      <c r="A23" s="90"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="75"/>
-      <c r="J23" s="84"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="71"/>
+      <c r="J23" s="72"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8481,16 +8481,11 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8507,11 +8502,16 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8531,7 +8531,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="81" t="s">
         <v>33</v>
       </c>
       <c r="B1" s="47"/>
@@ -8542,14 +8542,14 @@
       <c r="G1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
       <c r="J1" s="56"/>
       <c r="K1" s="55" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
+      <c r="L1" s="74"/>
+      <c r="M1" s="74"/>
       <c r="N1" s="56"/>
       <c r="O1" s="55" t="s">
         <v>7</v>
@@ -8562,7 +8562,7 @@
       <c r="S1" s="55" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="86"/>
+      <c r="T1" s="75"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
       <c r="A2" s="49"/>
@@ -8628,36 +8628,36 @@
       <c r="Q4" s="62"/>
       <c r="R4" s="54"/>
       <c r="S4" s="62"/>
-      <c r="T4" s="102"/>
+      <c r="T4" s="106"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="A5" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
       <c r="F5" s="56"/>
-      <c r="G5" s="85" t="s">
+      <c r="G5" s="73" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-      <c r="J5" s="79"/>
-      <c r="K5" s="79"/>
-      <c r="L5" s="79"/>
-      <c r="M5" s="79"/>
-      <c r="N5" s="79"/>
-      <c r="O5" s="79"/>
-      <c r="P5" s="79"/>
-      <c r="Q5" s="79"/>
-      <c r="R5" s="79"/>
-      <c r="S5" s="79"/>
-      <c r="T5" s="86"/>
+      <c r="H5" s="74"/>
+      <c r="I5" s="74"/>
+      <c r="J5" s="74"/>
+      <c r="K5" s="74"/>
+      <c r="L5" s="74"/>
+      <c r="M5" s="74"/>
+      <c r="N5" s="74"/>
+      <c r="O5" s="74"/>
+      <c r="P5" s="74"/>
+      <c r="Q5" s="74"/>
+      <c r="R5" s="74"/>
+      <c r="S5" s="74"/>
+      <c r="T5" s="75"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="91" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="64"/>
@@ -8665,7 +8665,7 @@
       <c r="D6" s="64"/>
       <c r="E6" s="64"/>
       <c r="F6" s="65"/>
-      <c r="G6" s="72" t="s">
+      <c r="G6" s="76" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="64"/>
@@ -8680,10 +8680,10 @@
       <c r="Q6" s="64"/>
       <c r="R6" s="64"/>
       <c r="S6" s="64"/>
-      <c r="T6" s="73"/>
+      <c r="T6" s="77"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="90" t="s">
+      <c r="A7" s="91" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="64"/>
@@ -8691,7 +8691,7 @@
       <c r="D7" s="64"/>
       <c r="E7" s="64"/>
       <c r="F7" s="65"/>
-      <c r="G7" s="72" t="s">
+      <c r="G7" s="76" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="64"/>
@@ -8706,7 +8706,7 @@
       <c r="Q7" s="64"/>
       <c r="R7" s="64"/>
       <c r="S7" s="64"/>
-      <c r="T7" s="73"/>
+      <c r="T7" s="77"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8905,7 +8905,7 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="91" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="65"/>
@@ -8947,33 +8947,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="103">
+      <c r="A16" s="98">
         <v>1</v>
       </c>
       <c r="B16" s="65"/>
-      <c r="C16" s="104" t="s">
+      <c r="C16" s="99" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="65"/>
-      <c r="E16" s="104" t="s">
+      <c r="E16" s="99" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="65"/>
-      <c r="G16" s="98" t="s">
+      <c r="G16" s="104" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="64"/>
       <c r="I16" s="65"/>
-      <c r="J16" s="98" t="s">
+      <c r="J16" s="104" t="s">
         <v>57</v>
       </c>
       <c r="K16" s="65"/>
-      <c r="L16" s="100" t="s">
+      <c r="L16" s="102" t="s">
         <v>58</v>
       </c>
       <c r="M16" s="64"/>
       <c r="N16" s="65"/>
-      <c r="O16" s="100" t="s">
+      <c r="O16" s="102" t="s">
         <v>59</v>
       </c>
       <c r="P16" s="64"/>
@@ -8989,33 +8989,33 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="103">
+      <c r="A17" s="98">
         <v>2</v>
       </c>
       <c r="B17" s="65"/>
-      <c r="C17" s="104" t="s">
+      <c r="C17" s="99" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="65"/>
-      <c r="E17" s="104" t="s">
+      <c r="E17" s="99" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="65"/>
-      <c r="G17" s="98" t="s">
+      <c r="G17" s="104" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="64"/>
       <c r="I17" s="65"/>
-      <c r="J17" s="98" t="s">
+      <c r="J17" s="104" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="65"/>
-      <c r="L17" s="100" t="s">
+      <c r="L17" s="102" t="s">
         <v>64</v>
       </c>
       <c r="M17" s="64"/>
       <c r="N17" s="65"/>
-      <c r="O17" s="100" t="s">
+      <c r="O17" s="102" t="s">
         <v>65</v>
       </c>
       <c r="P17" s="64"/>
@@ -9031,21 +9031,21 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="103"/>
+      <c r="A18" s="98"/>
       <c r="B18" s="65"/>
-      <c r="C18" s="104"/>
+      <c r="C18" s="99"/>
       <c r="D18" s="65"/>
-      <c r="E18" s="104"/>
+      <c r="E18" s="99"/>
       <c r="F18" s="65"/>
-      <c r="G18" s="98"/>
+      <c r="G18" s="104"/>
       <c r="H18" s="64"/>
       <c r="I18" s="65"/>
-      <c r="J18" s="98"/>
+      <c r="J18" s="104"/>
       <c r="K18" s="65"/>
-      <c r="L18" s="100"/>
+      <c r="L18" s="102"/>
       <c r="M18" s="64"/>
       <c r="N18" s="65"/>
-      <c r="O18" s="100"/>
+      <c r="O18" s="102"/>
       <c r="P18" s="64"/>
       <c r="Q18" s="65"/>
       <c r="R18" s="33"/>
@@ -9059,21 +9059,21 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="103"/>
+      <c r="A19" s="98"/>
       <c r="B19" s="65"/>
-      <c r="C19" s="104"/>
+      <c r="C19" s="99"/>
       <c r="D19" s="65"/>
-      <c r="E19" s="104"/>
+      <c r="E19" s="99"/>
       <c r="F19" s="65"/>
-      <c r="G19" s="98"/>
+      <c r="G19" s="104"/>
       <c r="H19" s="64"/>
       <c r="I19" s="65"/>
-      <c r="J19" s="98"/>
+      <c r="J19" s="104"/>
       <c r="K19" s="65"/>
-      <c r="L19" s="100"/>
+      <c r="L19" s="102"/>
       <c r="M19" s="64"/>
       <c r="N19" s="65"/>
-      <c r="O19" s="100"/>
+      <c r="O19" s="102"/>
       <c r="P19" s="64"/>
       <c r="Q19" s="65"/>
       <c r="R19" s="33"/>
@@ -9087,21 +9087,21 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="103"/>
+      <c r="A20" s="98"/>
       <c r="B20" s="65"/>
-      <c r="C20" s="104"/>
+      <c r="C20" s="99"/>
       <c r="D20" s="65"/>
-      <c r="E20" s="104"/>
+      <c r="E20" s="99"/>
       <c r="F20" s="65"/>
-      <c r="G20" s="98"/>
+      <c r="G20" s="104"/>
       <c r="H20" s="64"/>
       <c r="I20" s="65"/>
-      <c r="J20" s="98"/>
+      <c r="J20" s="104"/>
       <c r="K20" s="65"/>
-      <c r="L20" s="100"/>
+      <c r="L20" s="102"/>
       <c r="M20" s="64"/>
       <c r="N20" s="65"/>
-      <c r="O20" s="100"/>
+      <c r="O20" s="102"/>
       <c r="P20" s="64"/>
       <c r="Q20" s="65"/>
       <c r="R20" s="33"/>
@@ -9115,21 +9115,21 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="103"/>
+      <c r="A21" s="98"/>
       <c r="B21" s="65"/>
-      <c r="C21" s="104"/>
+      <c r="C21" s="99"/>
       <c r="D21" s="65"/>
-      <c r="E21" s="104"/>
+      <c r="E21" s="99"/>
       <c r="F21" s="65"/>
-      <c r="G21" s="98"/>
+      <c r="G21" s="104"/>
       <c r="H21" s="64"/>
       <c r="I21" s="65"/>
-      <c r="J21" s="98"/>
+      <c r="J21" s="104"/>
       <c r="K21" s="65"/>
-      <c r="L21" s="100"/>
+      <c r="L21" s="102"/>
       <c r="M21" s="64"/>
       <c r="N21" s="65"/>
-      <c r="O21" s="100"/>
+      <c r="O21" s="102"/>
       <c r="P21" s="64"/>
       <c r="Q21" s="65"/>
       <c r="R21" s="33"/>
@@ -9143,21 +9143,21 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="103"/>
+      <c r="A22" s="98"/>
       <c r="B22" s="65"/>
-      <c r="C22" s="104"/>
+      <c r="C22" s="99"/>
       <c r="D22" s="65"/>
-      <c r="E22" s="104"/>
+      <c r="E22" s="99"/>
       <c r="F22" s="65"/>
-      <c r="G22" s="98"/>
+      <c r="G22" s="104"/>
       <c r="H22" s="64"/>
       <c r="I22" s="65"/>
-      <c r="J22" s="98"/>
+      <c r="J22" s="104"/>
       <c r="K22" s="65"/>
-      <c r="L22" s="100"/>
+      <c r="L22" s="102"/>
       <c r="M22" s="64"/>
       <c r="N22" s="65"/>
-      <c r="O22" s="100"/>
+      <c r="O22" s="102"/>
       <c r="P22" s="64"/>
       <c r="Q22" s="65"/>
       <c r="R22" s="33"/>
@@ -9171,21 +9171,21 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="103"/>
+      <c r="A23" s="98"/>
       <c r="B23" s="65"/>
-      <c r="C23" s="104"/>
+      <c r="C23" s="99"/>
       <c r="D23" s="65"/>
-      <c r="E23" s="104"/>
+      <c r="E23" s="99"/>
       <c r="F23" s="65"/>
-      <c r="G23" s="98"/>
+      <c r="G23" s="104"/>
       <c r="H23" s="64"/>
       <c r="I23" s="65"/>
-      <c r="J23" s="98"/>
+      <c r="J23" s="104"/>
       <c r="K23" s="65"/>
-      <c r="L23" s="100"/>
+      <c r="L23" s="102"/>
       <c r="M23" s="64"/>
       <c r="N23" s="65"/>
-      <c r="O23" s="100"/>
+      <c r="O23" s="102"/>
       <c r="P23" s="64"/>
       <c r="Q23" s="65"/>
       <c r="R23" s="33"/>
@@ -9199,21 +9199,21 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="103"/>
+      <c r="A24" s="98"/>
       <c r="B24" s="65"/>
-      <c r="C24" s="104"/>
+      <c r="C24" s="99"/>
       <c r="D24" s="65"/>
-      <c r="E24" s="104"/>
+      <c r="E24" s="99"/>
       <c r="F24" s="65"/>
-      <c r="G24" s="98"/>
+      <c r="G24" s="104"/>
       <c r="H24" s="64"/>
       <c r="I24" s="65"/>
-      <c r="J24" s="98"/>
+      <c r="J24" s="104"/>
       <c r="K24" s="65"/>
-      <c r="L24" s="100"/>
+      <c r="L24" s="102"/>
       <c r="M24" s="64"/>
       <c r="N24" s="65"/>
-      <c r="O24" s="100"/>
+      <c r="O24" s="102"/>
       <c r="P24" s="64"/>
       <c r="Q24" s="65"/>
       <c r="R24" s="33"/>
@@ -9227,21 +9227,21 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="103"/>
+      <c r="A25" s="98"/>
       <c r="B25" s="65"/>
-      <c r="C25" s="104"/>
+      <c r="C25" s="99"/>
       <c r="D25" s="65"/>
-      <c r="E25" s="104"/>
+      <c r="E25" s="99"/>
       <c r="F25" s="65"/>
-      <c r="G25" s="98"/>
+      <c r="G25" s="104"/>
       <c r="H25" s="64"/>
       <c r="I25" s="65"/>
-      <c r="J25" s="98"/>
+      <c r="J25" s="104"/>
       <c r="K25" s="65"/>
-      <c r="L25" s="100"/>
+      <c r="L25" s="102"/>
       <c r="M25" s="64"/>
       <c r="N25" s="65"/>
-      <c r="O25" s="100"/>
+      <c r="O25" s="102"/>
       <c r="P25" s="64"/>
       <c r="Q25" s="65"/>
       <c r="R25" s="33"/>
@@ -9255,21 +9255,21 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="103"/>
+      <c r="A26" s="98"/>
       <c r="B26" s="65"/>
-      <c r="C26" s="104"/>
+      <c r="C26" s="99"/>
       <c r="D26" s="65"/>
-      <c r="E26" s="104"/>
+      <c r="E26" s="99"/>
       <c r="F26" s="65"/>
-      <c r="G26" s="98"/>
+      <c r="G26" s="104"/>
       <c r="H26" s="64"/>
       <c r="I26" s="65"/>
-      <c r="J26" s="98"/>
+      <c r="J26" s="104"/>
       <c r="K26" s="65"/>
-      <c r="L26" s="100"/>
+      <c r="L26" s="102"/>
       <c r="M26" s="64"/>
       <c r="N26" s="65"/>
-      <c r="O26" s="100"/>
+      <c r="O26" s="102"/>
       <c r="P26" s="64"/>
       <c r="Q26" s="65"/>
       <c r="R26" s="33"/>
@@ -9283,21 +9283,21 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="103"/>
+      <c r="A27" s="98"/>
       <c r="B27" s="65"/>
-      <c r="C27" s="104"/>
+      <c r="C27" s="99"/>
       <c r="D27" s="65"/>
-      <c r="E27" s="104"/>
+      <c r="E27" s="99"/>
       <c r="F27" s="65"/>
-      <c r="G27" s="98"/>
+      <c r="G27" s="104"/>
       <c r="H27" s="64"/>
       <c r="I27" s="65"/>
-      <c r="J27" s="98"/>
+      <c r="J27" s="104"/>
       <c r="K27" s="65"/>
-      <c r="L27" s="100"/>
+      <c r="L27" s="102"/>
       <c r="M27" s="64"/>
       <c r="N27" s="65"/>
-      <c r="O27" s="100"/>
+      <c r="O27" s="102"/>
       <c r="P27" s="64"/>
       <c r="Q27" s="65"/>
       <c r="R27" s="33"/>
@@ -9311,21 +9311,21 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="103"/>
+      <c r="A28" s="98"/>
       <c r="B28" s="65"/>
-      <c r="C28" s="104"/>
+      <c r="C28" s="99"/>
       <c r="D28" s="65"/>
-      <c r="E28" s="104"/>
+      <c r="E28" s="99"/>
       <c r="F28" s="65"/>
-      <c r="G28" s="98"/>
+      <c r="G28" s="104"/>
       <c r="H28" s="64"/>
       <c r="I28" s="65"/>
-      <c r="J28" s="98"/>
+      <c r="J28" s="104"/>
       <c r="K28" s="65"/>
-      <c r="L28" s="100"/>
+      <c r="L28" s="102"/>
       <c r="M28" s="64"/>
       <c r="N28" s="65"/>
-      <c r="O28" s="100"/>
+      <c r="O28" s="102"/>
       <c r="P28" s="64"/>
       <c r="Q28" s="65"/>
       <c r="R28" s="33"/>
@@ -9339,21 +9339,21 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="103"/>
+      <c r="A29" s="98"/>
       <c r="B29" s="65"/>
-      <c r="C29" s="104"/>
+      <c r="C29" s="99"/>
       <c r="D29" s="65"/>
-      <c r="E29" s="104"/>
+      <c r="E29" s="99"/>
       <c r="F29" s="65"/>
-      <c r="G29" s="98"/>
+      <c r="G29" s="104"/>
       <c r="H29" s="64"/>
       <c r="I29" s="65"/>
-      <c r="J29" s="98"/>
+      <c r="J29" s="104"/>
       <c r="K29" s="65"/>
-      <c r="L29" s="100"/>
+      <c r="L29" s="102"/>
       <c r="M29" s="64"/>
       <c r="N29" s="65"/>
-      <c r="O29" s="100"/>
+      <c r="O29" s="102"/>
       <c r="P29" s="64"/>
       <c r="Q29" s="65"/>
       <c r="R29" s="33"/>
@@ -9367,21 +9367,21 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="103"/>
+      <c r="A30" s="98"/>
       <c r="B30" s="65"/>
-      <c r="C30" s="104"/>
+      <c r="C30" s="99"/>
       <c r="D30" s="65"/>
-      <c r="E30" s="104"/>
+      <c r="E30" s="99"/>
       <c r="F30" s="65"/>
-      <c r="G30" s="98"/>
+      <c r="G30" s="104"/>
       <c r="H30" s="64"/>
       <c r="I30" s="65"/>
-      <c r="J30" s="98"/>
+      <c r="J30" s="104"/>
       <c r="K30" s="65"/>
-      <c r="L30" s="100"/>
+      <c r="L30" s="102"/>
       <c r="M30" s="64"/>
       <c r="N30" s="65"/>
-      <c r="O30" s="100"/>
+      <c r="O30" s="102"/>
       <c r="P30" s="64"/>
       <c r="Q30" s="65"/>
       <c r="R30" s="33"/>
@@ -9395,23 +9395,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="106"/>
-      <c r="B31" s="76"/>
-      <c r="C31" s="107"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="107"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="76"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="76"/>
-      <c r="L31" s="101"/>
-      <c r="M31" s="75"/>
-      <c r="N31" s="76"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="75"/>
-      <c r="Q31" s="76"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="80"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="80"/>
+      <c r="G31" s="107"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="80"/>
+      <c r="J31" s="107"/>
+      <c r="K31" s="80"/>
+      <c r="L31" s="103"/>
+      <c r="M31" s="71"/>
+      <c r="N31" s="80"/>
+      <c r="O31" s="103"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="80"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10409,6 +10409,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10433,118 +10545,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_ログアウト機能.xlsx
+++ b/document/成果物ドキュメント_ログアウト機能.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Documents\project\TaskManager62\document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskManager62\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1565A45-60DD-4B1C-AF7B-199D0054CFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445D78FF-F499-43A6-A3C1-6A06EDD024B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10245" yWindow="0" windowWidth="10245" windowHeight="10920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
@@ -34,9 +34,6 @@
   </si>
   <si>
     <t>YYYY/MM/DD</t>
-  </si>
-  <si>
-    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -339,58 +336,51 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログアウトされること</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>TaskManager62システム</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>1.ユーザーがメニュー画面を開く
-2.ユーザーがログアウトボタンを選択する
-3.システムがログイン情報を削除する
-4.システムがログアウト画面画面を表示する
-5.ユーザーがログイン画面へ戻るを選択する
-6.システムがログイン画面を表示する</t>
-    <rPh sb="11" eb="13">
+    <t>1.ユーザーがログアウトを選択する
+2.システムがログアウト画面画面を表示する
+3.ユーザーがログイン画面へ戻るを選択する
+4.システムがログイン画面を表示する</t>
+    <rPh sb="13" eb="15">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="30" eb="32">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="14" eb="15">
-      <t>ヒラ</t>
+    <rPh sb="32" eb="34">
+      <t>ガメン</t>
     </rPh>
-    <rPh sb="33" eb="35">
+    <rPh sb="35" eb="37">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="51" eb="53">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="54" eb="55">
+      <t>モド</t>
+    </rPh>
+    <rPh sb="57" eb="59">
       <t>センタク</t>
     </rPh>
-    <rPh sb="49" eb="51">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="69" eb="71">
+    <rPh sb="73" eb="75">
       <t>ガメン</t>
     </rPh>
-    <rPh sb="71" eb="73">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="74" eb="76">
+    <rPh sb="76" eb="78">
       <t>ヒョウジ</t>
     </rPh>
-    <rPh sb="90" eb="92">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="93" eb="94">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="96" eb="98">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="112" eb="114">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="115" eb="117">
-      <t>ヒョウジ</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログアウトする</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>チーム名 62期</t>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -1293,6 +1283,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1314,144 +1328,120 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1470,35 +1460,35 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1922,85 +1912,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-      <c r="O2" s="68"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="50"/>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="50"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="67"/>
+      <c r="O3" s="67"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
-      <c r="E4" s="50"/>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="50"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="50"/>
-      <c r="N4" s="50"/>
-      <c r="O4" s="50"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
+      <c r="I4" s="67"/>
+      <c r="J4" s="67"/>
+      <c r="K4" s="67"/>
+      <c r="L4" s="67"/>
+      <c r="M4" s="67"/>
+      <c r="N4" s="67"/>
+      <c r="O4" s="67"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
+      <c r="L5" s="67"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="50"/>
-      <c r="N6" s="50"/>
-      <c r="O6" s="50"/>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+      <c r="G6" s="67"/>
+      <c r="H6" s="67"/>
+      <c r="I6" s="67"/>
+      <c r="J6" s="67"/>
+      <c r="K6" s="67"/>
+      <c r="L6" s="67"/>
+      <c r="M6" s="67"/>
+      <c r="N6" s="67"/>
+      <c r="O6" s="67"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2020,46 +2010,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="69" t="s">
-        <v>84</v>
-      </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
+      <c r="E8" s="84" t="s">
+        <v>82</v>
+      </c>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
+      <c r="J8" s="67"/>
+      <c r="K8" s="67"/>
+      <c r="L8" s="67"/>
+      <c r="M8" s="67"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="63" t="s">
+      <c r="G13" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="65"/>
-      <c r="I13" s="63" t="s">
+      <c r="H13" s="55"/>
+      <c r="I13" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="J13" s="64"/>
-      <c r="K13" s="65"/>
+      <c r="J13" s="57"/>
+      <c r="K13" s="55"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="63"/>
-      <c r="H14" s="65"/>
-      <c r="I14" s="63"/>
-      <c r="J14" s="64"/>
-      <c r="K14" s="65"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="55"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="57"/>
+      <c r="K14" s="55"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="63"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="64"/>
-      <c r="K15" s="65"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="57"/>
+      <c r="K15" s="55"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2068,13 +2058,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="66" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="50"/>
-      <c r="I17" s="50"/>
-      <c r="J17" s="50"/>
-      <c r="K17" s="50"/>
+      <c r="G17" s="81" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="67"/>
+      <c r="I17" s="67"/>
+      <c r="J17" s="67"/>
+      <c r="K17" s="67"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3088,216 +3078,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="39" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
+      <c r="E1" s="40"/>
+      <c r="F1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="G1" s="40"/>
+      <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="56"/>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="42"/>
+      <c r="F2" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="G2" s="42"/>
+      <c r="H2" s="47">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="51"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="52"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="68"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="53"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="70" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="39">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="42" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="43"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="45"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="82" t="s">
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="78"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="73" t="s">
+      <c r="B6" s="57"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="59"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="57"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="58" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="75"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="83" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="76" t="s">
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="59"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="56" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="57"/>
+      <c r="C8" s="55"/>
+      <c r="D8" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
+      <c r="J8" s="59"/>
+    </row>
+    <row r="9" spans="1:10" ht="91.5" customHeight="1">
+      <c r="A9" s="72" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="54" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="55"/>
+      <c r="D9" s="79" t="s">
         <v>83</v>
       </c>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="77"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="83" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="65"/>
-      <c r="D7" s="76" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="64"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="77"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="83" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="64"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="76" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="64"/>
-      <c r="F8" s="64"/>
-      <c r="G8" s="64"/>
-      <c r="H8" s="64"/>
-      <c r="I8" s="64"/>
-      <c r="J8" s="77"/>
-    </row>
-    <row r="9" spans="1:10" ht="91.5" customHeight="1">
-      <c r="A9" s="84" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="87" t="s">
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
+      <c r="J9" s="59"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="73"/>
+      <c r="B10" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="D9" s="78" t="s">
-        <v>85</v>
-      </c>
-      <c r="E9" s="64"/>
-      <c r="F9" s="64"/>
-      <c r="G9" s="64"/>
-      <c r="H9" s="64"/>
-      <c r="I9" s="64"/>
-      <c r="J9" s="77"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="85"/>
-      <c r="B10" s="87" t="s">
+      <c r="C10" s="55"/>
+      <c r="D10" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
+      <c r="J10" s="59"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="74"/>
+      <c r="B11" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="65"/>
-      <c r="D10" s="76" t="s">
+      <c r="C11" s="55"/>
+      <c r="D11" s="58" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
+      <c r="J11" s="59"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="56" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="57"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="58" t="s">
         <v>80</v>
       </c>
-      <c r="E10" s="64"/>
-      <c r="F10" s="64"/>
-      <c r="G10" s="64"/>
-      <c r="H10" s="64"/>
-      <c r="I10" s="64"/>
-      <c r="J10" s="77"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="86"/>
-      <c r="B11" s="87" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="76" t="s">
-        <v>80</v>
-      </c>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
-      <c r="G11" s="64"/>
-      <c r="H11" s="64"/>
-      <c r="I11" s="64"/>
-      <c r="J11" s="77"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="83" t="s">
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
+      <c r="J12" s="59"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="64"/>
-      <c r="C12" s="65"/>
-      <c r="D12" s="76" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
-      <c r="G12" s="64"/>
-      <c r="H12" s="64"/>
-      <c r="I12" s="64"/>
-      <c r="J12" s="77"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="79" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="71"/>
-      <c r="C13" s="80"/>
-      <c r="D13" s="70"/>
-      <c r="E13" s="71"/>
-      <c r="F13" s="71"/>
-      <c r="G13" s="71"/>
-      <c r="H13" s="71"/>
-      <c r="I13" s="71"/>
-      <c r="J13" s="72"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="75"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="76"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4288,17 +4278,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4307,14 +4294,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4333,72 +4323,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
+      <c r="A1" s="85" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="40"/>
+      <c r="F1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="G1" s="40"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="56"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="42"/>
+      <c r="F2" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
+      <c r="G2" s="42"/>
+      <c r="H2" s="47">
+        <v>46120</v>
+      </c>
+      <c r="I2" s="50" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="39">
-        <v>46120</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="43"/>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="62"/>
-      <c r="E4" s="54"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="45"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="46"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5753,72 +5743,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
+      <c r="A1" s="85" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="40"/>
+      <c r="F1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
+      <c r="G1" s="40"/>
+      <c r="H1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="56"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="42"/>
+      <c r="F2" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="39">
+      <c r="G2" s="42"/>
+      <c r="H2" s="47">
         <v>46121</v>
       </c>
-      <c r="I2" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="43"/>
+      <c r="I2" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="51"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="52"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="61"/>
-      <c r="F4" s="62"/>
-      <c r="G4" s="54"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
-      <c r="J4" s="45"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="86"/>
+      <c r="E4" s="87"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7169,102 +7159,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="85" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="40"/>
+      <c r="F1" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="40"/>
+      <c r="H1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="42"/>
+      <c r="F2" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="42"/>
+      <c r="H2" s="47">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="50" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="51"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="44"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="52"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="66"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="43"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="52"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="56"/>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="57" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="58"/>
-      <c r="F2" s="57" t="s">
+      <c r="B5" s="71"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="92" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="39">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="42" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="43"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="44"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="49"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="59"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="40"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="44"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="89" t="s">
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="78"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="56"/>
-      <c r="D5" s="92" t="s">
-        <v>73</v>
-      </c>
-      <c r="E5" s="74"/>
-      <c r="F5" s="74"/>
-      <c r="G5" s="74"/>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="75"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="91" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
-      <c r="G6" s="64"/>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="77"/>
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="59"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="93"/>
@@ -7279,228 +7269,228 @@
       <c r="J7" s="95"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="49"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
+      <c r="A8" s="66"/>
+      <c r="B8" s="67"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="67"/>
+      <c r="H8" s="67"/>
+      <c r="I8" s="67"/>
       <c r="J8" s="96"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="49"/>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="50"/>
+      <c r="A9" s="66"/>
+      <c r="B9" s="67"/>
+      <c r="C9" s="67"/>
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
       <c r="J9" s="96"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="49"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
+      <c r="A10" s="66"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
       <c r="J10" s="96"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="49"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
+      <c r="A11" s="66"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
       <c r="J11" s="96"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="49"/>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="50"/>
+      <c r="A12" s="66"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
       <c r="J12" s="96"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="49"/>
-      <c r="B13" s="50"/>
-      <c r="C13" s="50"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
+      <c r="A13" s="66"/>
+      <c r="B13" s="67"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="67"/>
+      <c r="F13" s="67"/>
+      <c r="G13" s="67"/>
+      <c r="H13" s="67"/>
+      <c r="I13" s="67"/>
       <c r="J13" s="96"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="91" t="s">
+      <c r="A14" s="90" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
+      <c r="J14" s="59"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="90" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="64"/>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
-      <c r="I14" s="64"/>
-      <c r="J14" s="77"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="91" t="s">
+      <c r="B15" s="57"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="76" t="s">
+      <c r="J15" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="90" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="57"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="97" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="57"/>
+      <c r="J16" s="59"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="91" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
-      <c r="G15" s="64"/>
-      <c r="H15" s="65"/>
-      <c r="I15" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="91" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="64"/>
-      <c r="C16" s="65"/>
-      <c r="D16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="97" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="64"/>
-      <c r="J16" s="77"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="88" t="s">
+      <c r="B17" s="57"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>76</v>
-      </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="65"/>
-      <c r="D17" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>77</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="76" t="s">
-        <v>79</v>
-      </c>
-      <c r="I17" s="64"/>
-      <c r="J17" s="77"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="59"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="88"/>
-      <c r="B18" s="64"/>
-      <c r="C18" s="65"/>
+      <c r="A18" s="91"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="55"/>
       <c r="D18" s="17"/>
       <c r="E18" s="17"/>
       <c r="F18" s="18"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="76"/>
-      <c r="I18" s="64"/>
-      <c r="J18" s="77"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="57"/>
+      <c r="J18" s="59"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="88"/>
-      <c r="B19" s="64"/>
-      <c r="C19" s="65"/>
+      <c r="A19" s="91"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="55"/>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="18"/>
       <c r="G19" s="18"/>
-      <c r="H19" s="76"/>
-      <c r="I19" s="64"/>
-      <c r="J19" s="77"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="59"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="88"/>
-      <c r="B20" s="64"/>
-      <c r="C20" s="65"/>
+      <c r="A20" s="91"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="55"/>
       <c r="D20" s="17"/>
       <c r="E20" s="17"/>
       <c r="F20" s="18"/>
       <c r="G20" s="18"/>
-      <c r="H20" s="76"/>
-      <c r="I20" s="64"/>
-      <c r="J20" s="77"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="57"/>
+      <c r="J20" s="59"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="88"/>
-      <c r="B21" s="64"/>
-      <c r="C21" s="65"/>
+      <c r="A21" s="91"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="55"/>
       <c r="D21" s="17"/>
       <c r="E21" s="17"/>
       <c r="F21" s="18"/>
       <c r="G21" s="18"/>
-      <c r="H21" s="76"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="77"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="57"/>
+      <c r="J21" s="59"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="88"/>
-      <c r="B22" s="64"/>
-      <c r="C22" s="65"/>
+      <c r="A22" s="91"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="55"/>
       <c r="D22" s="17"/>
       <c r="E22" s="17"/>
       <c r="F22" s="18"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="64"/>
-      <c r="J22" s="77"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="57"/>
+      <c r="J22" s="59"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="90"/>
-      <c r="B23" s="71"/>
-      <c r="C23" s="80"/>
+      <c r="A23" s="89"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="62"/>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
       <c r="F23" s="20"/>
       <c r="G23" s="20"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="71"/>
-      <c r="J23" s="72"/>
+      <c r="H23" s="75"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="76"/>
     </row>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8481,11 +8471,16 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H19:J19"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -8502,16 +8497,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8531,182 +8521,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="55" t="s">
+      <c r="A1" s="63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
-      <c r="J1" s="56"/>
-      <c r="K1" s="55" t="s">
+      <c r="L1" s="71"/>
+      <c r="M1" s="71"/>
+      <c r="N1" s="40"/>
+      <c r="O1" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="74"/>
-      <c r="M1" s="74"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="55" t="s">
+      <c r="P1" s="40"/>
+      <c r="Q1" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="56"/>
-      <c r="Q1" s="55" t="s">
+      <c r="R1" s="40"/>
+      <c r="S1" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="56"/>
-      <c r="S1" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="75"/>
+      <c r="T1" s="78"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="57"/>
+      <c r="A2" s="66"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="41"/>
       <c r="H2" s="94"/>
       <c r="I2" s="94"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="57"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="41"/>
       <c r="L2" s="94"/>
       <c r="M2" s="94"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="57"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="41"/>
       <c r="T2" s="95"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
-      <c r="E3" s="50"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="59"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="50"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="59"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="59"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="59"/>
+      <c r="A3" s="66"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="44"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="44"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="67"/>
+      <c r="M3" s="67"/>
+      <c r="N3" s="44"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="44"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="44"/>
+      <c r="S3" s="43"/>
       <c r="T3" s="96"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="54"/>
-      <c r="G4" s="62"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="54"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="53"/>
-      <c r="M4" s="53"/>
-      <c r="N4" s="54"/>
-      <c r="O4" s="62"/>
-      <c r="P4" s="54"/>
-      <c r="Q4" s="62"/>
-      <c r="R4" s="54"/>
-      <c r="S4" s="62"/>
-      <c r="T4" s="106"/>
+      <c r="A4" s="68"/>
+      <c r="B4" s="69"/>
+      <c r="C4" s="69"/>
+      <c r="D4" s="69"/>
+      <c r="E4" s="69"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="69"/>
+      <c r="I4" s="69"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="69"/>
+      <c r="M4" s="69"/>
+      <c r="N4" s="46"/>
+      <c r="O4" s="45"/>
+      <c r="P4" s="46"/>
+      <c r="Q4" s="45"/>
+      <c r="R4" s="46"/>
+      <c r="S4" s="45"/>
+      <c r="T4" s="102"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="89" t="s">
+      <c r="A5" s="88" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="71"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="56"/>
-      <c r="G5" s="73" t="s">
+      <c r="H5" s="71"/>
+      <c r="I5" s="71"/>
+      <c r="J5" s="71"/>
+      <c r="K5" s="71"/>
+      <c r="L5" s="71"/>
+      <c r="M5" s="71"/>
+      <c r="N5" s="71"/>
+      <c r="O5" s="71"/>
+      <c r="P5" s="71"/>
+      <c r="Q5" s="71"/>
+      <c r="R5" s="71"/>
+      <c r="S5" s="71"/>
+      <c r="T5" s="78"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="90" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="74"/>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="74"/>
-      <c r="L5" s="74"/>
-      <c r="M5" s="74"/>
-      <c r="N5" s="74"/>
-      <c r="O5" s="74"/>
-      <c r="P5" s="74"/>
-      <c r="Q5" s="74"/>
-      <c r="R5" s="74"/>
-      <c r="S5" s="74"/>
-      <c r="T5" s="75"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="91" t="s">
+      <c r="B6" s="57"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
+      <c r="J6" s="57"/>
+      <c r="K6" s="57"/>
+      <c r="L6" s="57"/>
+      <c r="M6" s="57"/>
+      <c r="N6" s="57"/>
+      <c r="O6" s="57"/>
+      <c r="P6" s="57"/>
+      <c r="Q6" s="57"/>
+      <c r="R6" s="57"/>
+      <c r="S6" s="57"/>
+      <c r="T6" s="59"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="90" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="76" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="64"/>
-      <c r="I6" s="64"/>
-      <c r="J6" s="64"/>
-      <c r="K6" s="64"/>
-      <c r="L6" s="64"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="64"/>
-      <c r="O6" s="64"/>
-      <c r="P6" s="64"/>
-      <c r="Q6" s="64"/>
-      <c r="R6" s="64"/>
-      <c r="S6" s="64"/>
-      <c r="T6" s="77"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="91" t="s">
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="64"/>
-      <c r="C7" s="64"/>
-      <c r="D7" s="64"/>
-      <c r="E7" s="64"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="64"/>
-      <c r="I7" s="64"/>
-      <c r="J7" s="64"/>
-      <c r="K7" s="64"/>
-      <c r="L7" s="64"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="64"/>
-      <c r="O7" s="64"/>
-      <c r="P7" s="64"/>
-      <c r="Q7" s="64"/>
-      <c r="R7" s="64"/>
-      <c r="S7" s="64"/>
-      <c r="T7" s="77"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
+      <c r="J7" s="57"/>
+      <c r="K7" s="57"/>
+      <c r="L7" s="57"/>
+      <c r="M7" s="57"/>
+      <c r="N7" s="57"/>
+      <c r="O7" s="57"/>
+      <c r="P7" s="57"/>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="57"/>
+      <c r="S7" s="57"/>
+      <c r="T7" s="59"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8734,11 +8724,11 @@
       <c r="A9" s="21"/>
       <c r="B9" s="22"/>
       <c r="C9" s="23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D9" s="24"/>
       <c r="E9" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F9" s="24"/>
       <c r="G9" s="25"/>
@@ -8768,7 +8758,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="22"/>
       <c r="E10" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="28"/>
@@ -8798,7 +8788,7 @@
       <c r="C11" s="27"/>
       <c r="D11" s="22"/>
       <c r="E11" s="22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="28"/>
@@ -8828,7 +8818,7 @@
       <c r="C12" s="27"/>
       <c r="D12" s="22"/>
       <c r="E12" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="28"/>
@@ -8858,7 +8848,7 @@
       <c r="C13" s="29"/>
       <c r="D13" s="30"/>
       <c r="E13" s="30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F13" s="30"/>
       <c r="G13" s="31"/>
@@ -8905,79 +8895,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="91" t="s">
+      <c r="A15" s="90" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="55"/>
+      <c r="C15" s="105" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="55"/>
+      <c r="E15" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="65"/>
-      <c r="C15" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="65"/>
-      <c r="E15" s="97" t="s">
+      <c r="F15" s="55"/>
+      <c r="G15" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="65"/>
-      <c r="G15" s="97" t="s">
+      <c r="H15" s="57"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="64"/>
-      <c r="I15" s="65"/>
-      <c r="J15" s="97" t="s">
+      <c r="K15" s="55"/>
+      <c r="L15" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="65"/>
-      <c r="L15" s="97" t="s">
+      <c r="M15" s="57"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="64"/>
-      <c r="N15" s="65"/>
-      <c r="O15" s="97" t="s">
+      <c r="P15" s="57"/>
+      <c r="Q15" s="55"/>
+      <c r="R15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="64"/>
-      <c r="Q15" s="65"/>
-      <c r="R15" s="15" t="s">
+      <c r="S15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="32" t="s">
         <v>52</v>
       </c>
-      <c r="T15" s="32" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="103">
+        <v>1</v>
+      </c>
+      <c r="B16" s="55"/>
+      <c r="C16" s="104" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="98">
-        <v>1</v>
-      </c>
-      <c r="B16" s="65"/>
-      <c r="C16" s="99" t="s">
+      <c r="D16" s="55"/>
+      <c r="E16" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="65"/>
-      <c r="E16" s="99" t="s">
+      <c r="F16" s="55"/>
+      <c r="G16" s="98" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="104" t="s">
+      <c r="H16" s="57"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="64"/>
-      <c r="I16" s="65"/>
-      <c r="J16" s="104" t="s">
+      <c r="K16" s="55"/>
+      <c r="L16" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="65"/>
-      <c r="L16" s="102" t="s">
+      <c r="M16" s="57"/>
+      <c r="N16" s="55"/>
+      <c r="O16" s="100" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="64"/>
-      <c r="N16" s="65"/>
-      <c r="O16" s="102" t="s">
-        <v>59</v>
-      </c>
-      <c r="P16" s="64"/>
-      <c r="Q16" s="65"/>
+      <c r="P16" s="57"/>
+      <c r="Q16" s="55"/>
       <c r="R16" s="33"/>
       <c r="S16" s="33"/>
       <c r="T16" s="34"/>
@@ -8989,37 +8979,37 @@
       <c r="Z16" s="35"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="98">
+      <c r="A17" s="103">
         <v>2</v>
       </c>
-      <c r="B17" s="65"/>
-      <c r="C17" s="99" t="s">
+      <c r="B17" s="55"/>
+      <c r="C17" s="104" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="55"/>
+      <c r="E17" s="104" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="65"/>
-      <c r="E17" s="99" t="s">
+      <c r="F17" s="55"/>
+      <c r="G17" s="98" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="104" t="s">
+      <c r="H17" s="57"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="64"/>
-      <c r="I17" s="65"/>
-      <c r="J17" s="104" t="s">
+      <c r="K17" s="55"/>
+      <c r="L17" s="100" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="65"/>
-      <c r="L17" s="102" t="s">
+      <c r="M17" s="57"/>
+      <c r="N17" s="55"/>
+      <c r="O17" s="100" t="s">
         <v>64</v>
       </c>
-      <c r="M17" s="64"/>
-      <c r="N17" s="65"/>
-      <c r="O17" s="102" t="s">
-        <v>65</v>
-      </c>
-      <c r="P17" s="64"/>
-      <c r="Q17" s="65"/>
+      <c r="P17" s="57"/>
+      <c r="Q17" s="55"/>
       <c r="R17" s="33"/>
       <c r="S17" s="33"/>
       <c r="T17" s="34"/>
@@ -9031,23 +9021,23 @@
       <c r="Z17" s="35"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="98"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="99"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="99"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="64"/>
-      <c r="I18" s="65"/>
-      <c r="J18" s="104"/>
-      <c r="K18" s="65"/>
-      <c r="L18" s="102"/>
-      <c r="M18" s="64"/>
-      <c r="N18" s="65"/>
-      <c r="O18" s="102"/>
-      <c r="P18" s="64"/>
-      <c r="Q18" s="65"/>
+      <c r="A18" s="103"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="55"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="98"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="55"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="55"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="57"/>
+      <c r="N18" s="55"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="55"/>
       <c r="R18" s="33"/>
       <c r="S18" s="33"/>
       <c r="T18" s="34"/>
@@ -9059,23 +9049,23 @@
       <c r="Z18" s="35"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="98"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="99"/>
-      <c r="D19" s="65"/>
-      <c r="E19" s="99"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="104"/>
-      <c r="H19" s="64"/>
-      <c r="I19" s="65"/>
-      <c r="J19" s="104"/>
-      <c r="K19" s="65"/>
-      <c r="L19" s="102"/>
-      <c r="M19" s="64"/>
-      <c r="N19" s="65"/>
-      <c r="O19" s="102"/>
-      <c r="P19" s="64"/>
-      <c r="Q19" s="65"/>
+      <c r="A19" s="103"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="55"/>
+      <c r="E19" s="104"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="98"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="55"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="55"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="57"/>
+      <c r="N19" s="55"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="57"/>
+      <c r="Q19" s="55"/>
       <c r="R19" s="33"/>
       <c r="S19" s="33"/>
       <c r="T19" s="34"/>
@@ -9087,23 +9077,23 @@
       <c r="Z19" s="35"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="98"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="65"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="65"/>
-      <c r="G20" s="104"/>
-      <c r="H20" s="64"/>
-      <c r="I20" s="65"/>
-      <c r="J20" s="104"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="102"/>
-      <c r="M20" s="64"/>
-      <c r="N20" s="65"/>
-      <c r="O20" s="102"/>
-      <c r="P20" s="64"/>
-      <c r="Q20" s="65"/>
+      <c r="A20" s="103"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="104"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="104"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="55"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="55"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="57"/>
+      <c r="N20" s="55"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="57"/>
+      <c r="Q20" s="55"/>
       <c r="R20" s="33"/>
       <c r="S20" s="33"/>
       <c r="T20" s="34"/>
@@ -9115,23 +9105,23 @@
       <c r="Z20" s="35"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="98"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="99"/>
-      <c r="D21" s="65"/>
-      <c r="E21" s="99"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="104"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="65"/>
-      <c r="J21" s="104"/>
-      <c r="K21" s="65"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="65"/>
-      <c r="O21" s="102"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="65"/>
+      <c r="A21" s="103"/>
+      <c r="B21" s="55"/>
+      <c r="C21" s="104"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="104"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="55"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="55"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="57"/>
+      <c r="N21" s="55"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="57"/>
+      <c r="Q21" s="55"/>
       <c r="R21" s="33"/>
       <c r="S21" s="33"/>
       <c r="T21" s="34"/>
@@ -9143,23 +9133,23 @@
       <c r="Z21" s="35"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="98"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="99"/>
-      <c r="D22" s="65"/>
-      <c r="E22" s="99"/>
-      <c r="F22" s="65"/>
-      <c r="G22" s="104"/>
-      <c r="H22" s="64"/>
-      <c r="I22" s="65"/>
-      <c r="J22" s="104"/>
-      <c r="K22" s="65"/>
-      <c r="L22" s="102"/>
-      <c r="M22" s="64"/>
-      <c r="N22" s="65"/>
-      <c r="O22" s="102"/>
-      <c r="P22" s="64"/>
-      <c r="Q22" s="65"/>
+      <c r="A22" s="103"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="104"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="55"/>
+      <c r="J22" s="98"/>
+      <c r="K22" s="55"/>
+      <c r="L22" s="100"/>
+      <c r="M22" s="57"/>
+      <c r="N22" s="55"/>
+      <c r="O22" s="100"/>
+      <c r="P22" s="57"/>
+      <c r="Q22" s="55"/>
       <c r="R22" s="33"/>
       <c r="S22" s="33"/>
       <c r="T22" s="34"/>
@@ -9171,23 +9161,23 @@
       <c r="Z22" s="35"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="98"/>
-      <c r="B23" s="65"/>
-      <c r="C23" s="99"/>
-      <c r="D23" s="65"/>
-      <c r="E23" s="99"/>
-      <c r="F23" s="65"/>
-      <c r="G23" s="104"/>
-      <c r="H23" s="64"/>
-      <c r="I23" s="65"/>
-      <c r="J23" s="104"/>
-      <c r="K23" s="65"/>
-      <c r="L23" s="102"/>
-      <c r="M23" s="64"/>
-      <c r="N23" s="65"/>
-      <c r="O23" s="102"/>
-      <c r="P23" s="64"/>
-      <c r="Q23" s="65"/>
+      <c r="A23" s="103"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="55"/>
+      <c r="J23" s="98"/>
+      <c r="K23" s="55"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="57"/>
+      <c r="N23" s="55"/>
+      <c r="O23" s="100"/>
+      <c r="P23" s="57"/>
+      <c r="Q23" s="55"/>
       <c r="R23" s="33"/>
       <c r="S23" s="33"/>
       <c r="T23" s="34"/>
@@ -9199,23 +9189,23 @@
       <c r="Z23" s="35"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="98"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="99"/>
-      <c r="D24" s="65"/>
-      <c r="E24" s="99"/>
-      <c r="F24" s="65"/>
-      <c r="G24" s="104"/>
-      <c r="H24" s="64"/>
-      <c r="I24" s="65"/>
-      <c r="J24" s="104"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="102"/>
-      <c r="M24" s="64"/>
-      <c r="N24" s="65"/>
-      <c r="O24" s="102"/>
-      <c r="P24" s="64"/>
-      <c r="Q24" s="65"/>
+      <c r="A24" s="103"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="104"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="104"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="57"/>
+      <c r="N24" s="55"/>
+      <c r="O24" s="100"/>
+      <c r="P24" s="57"/>
+      <c r="Q24" s="55"/>
       <c r="R24" s="33"/>
       <c r="S24" s="33"/>
       <c r="T24" s="34"/>
@@ -9227,23 +9217,23 @@
       <c r="Z24" s="35"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="98"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="65"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="65"/>
-      <c r="G25" s="104"/>
-      <c r="H25" s="64"/>
-      <c r="I25" s="65"/>
-      <c r="J25" s="104"/>
-      <c r="K25" s="65"/>
-      <c r="L25" s="102"/>
-      <c r="M25" s="64"/>
-      <c r="N25" s="65"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="64"/>
-      <c r="Q25" s="65"/>
+      <c r="A25" s="103"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="104"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="104"/>
+      <c r="F25" s="55"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="55"/>
+      <c r="J25" s="98"/>
+      <c r="K25" s="55"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="57"/>
+      <c r="N25" s="55"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="57"/>
+      <c r="Q25" s="55"/>
       <c r="R25" s="33"/>
       <c r="S25" s="33"/>
       <c r="T25" s="34"/>
@@ -9255,23 +9245,23 @@
       <c r="Z25" s="35"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="98"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="99"/>
-      <c r="D26" s="65"/>
-      <c r="E26" s="99"/>
-      <c r="F26" s="65"/>
-      <c r="G26" s="104"/>
-      <c r="H26" s="64"/>
-      <c r="I26" s="65"/>
-      <c r="J26" s="104"/>
-      <c r="K26" s="65"/>
-      <c r="L26" s="102"/>
-      <c r="M26" s="64"/>
-      <c r="N26" s="65"/>
-      <c r="O26" s="102"/>
-      <c r="P26" s="64"/>
-      <c r="Q26" s="65"/>
+      <c r="A26" s="103"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="104"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="104"/>
+      <c r="F26" s="55"/>
+      <c r="G26" s="98"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="55"/>
+      <c r="J26" s="98"/>
+      <c r="K26" s="55"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="57"/>
+      <c r="N26" s="55"/>
+      <c r="O26" s="100"/>
+      <c r="P26" s="57"/>
+      <c r="Q26" s="55"/>
       <c r="R26" s="33"/>
       <c r="S26" s="33"/>
       <c r="T26" s="34"/>
@@ -9283,23 +9273,23 @@
       <c r="Z26" s="35"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="98"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="99"/>
-      <c r="D27" s="65"/>
-      <c r="E27" s="99"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="104"/>
-      <c r="H27" s="64"/>
-      <c r="I27" s="65"/>
-      <c r="J27" s="104"/>
-      <c r="K27" s="65"/>
-      <c r="L27" s="102"/>
-      <c r="M27" s="64"/>
-      <c r="N27" s="65"/>
-      <c r="O27" s="102"/>
-      <c r="P27" s="64"/>
-      <c r="Q27" s="65"/>
+      <c r="A27" s="103"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="104"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="104"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="98"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="57"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="100"/>
+      <c r="P27" s="57"/>
+      <c r="Q27" s="55"/>
       <c r="R27" s="33"/>
       <c r="S27" s="33"/>
       <c r="T27" s="34"/>
@@ -9311,23 +9301,23 @@
       <c r="Z27" s="35"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="98"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="99"/>
-      <c r="D28" s="65"/>
-      <c r="E28" s="99"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="104"/>
-      <c r="H28" s="64"/>
-      <c r="I28" s="65"/>
-      <c r="J28" s="104"/>
-      <c r="K28" s="65"/>
-      <c r="L28" s="102"/>
-      <c r="M28" s="64"/>
-      <c r="N28" s="65"/>
-      <c r="O28" s="102"/>
-      <c r="P28" s="64"/>
-      <c r="Q28" s="65"/>
+      <c r="A28" s="103"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="104"/>
+      <c r="F28" s="55"/>
+      <c r="G28" s="98"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="55"/>
+      <c r="J28" s="98"/>
+      <c r="K28" s="55"/>
+      <c r="L28" s="100"/>
+      <c r="M28" s="57"/>
+      <c r="N28" s="55"/>
+      <c r="O28" s="100"/>
+      <c r="P28" s="57"/>
+      <c r="Q28" s="55"/>
       <c r="R28" s="33"/>
       <c r="S28" s="33"/>
       <c r="T28" s="34"/>
@@ -9339,23 +9329,23 @@
       <c r="Z28" s="35"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="98"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="99"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="99"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="104"/>
-      <c r="H29" s="64"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="104"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="102"/>
-      <c r="M29" s="64"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="102"/>
-      <c r="P29" s="64"/>
-      <c r="Q29" s="65"/>
+      <c r="A29" s="103"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="104"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="104"/>
+      <c r="F29" s="55"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="55"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="55"/>
+      <c r="L29" s="100"/>
+      <c r="M29" s="57"/>
+      <c r="N29" s="55"/>
+      <c r="O29" s="100"/>
+      <c r="P29" s="57"/>
+      <c r="Q29" s="55"/>
       <c r="R29" s="33"/>
       <c r="S29" s="33"/>
       <c r="T29" s="34"/>
@@ -9367,23 +9357,23 @@
       <c r="Z29" s="35"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="98"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="99"/>
-      <c r="D30" s="65"/>
-      <c r="E30" s="99"/>
-      <c r="F30" s="65"/>
-      <c r="G30" s="104"/>
-      <c r="H30" s="64"/>
-      <c r="I30" s="65"/>
-      <c r="J30" s="104"/>
-      <c r="K30" s="65"/>
-      <c r="L30" s="102"/>
-      <c r="M30" s="64"/>
-      <c r="N30" s="65"/>
-      <c r="O30" s="102"/>
-      <c r="P30" s="64"/>
-      <c r="Q30" s="65"/>
+      <c r="A30" s="103"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="104"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="104"/>
+      <c r="F30" s="55"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="55"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="55"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="55"/>
+      <c r="O30" s="100"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="55"/>
       <c r="R30" s="33"/>
       <c r="S30" s="33"/>
       <c r="T30" s="34"/>
@@ -9395,23 +9385,23 @@
       <c r="Z30" s="35"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="100"/>
-      <c r="B31" s="80"/>
-      <c r="C31" s="101"/>
-      <c r="D31" s="80"/>
-      <c r="E31" s="101"/>
-      <c r="F31" s="80"/>
-      <c r="G31" s="107"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="80"/>
-      <c r="J31" s="107"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="103"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="80"/>
-      <c r="O31" s="103"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="80"/>
+      <c r="A31" s="106"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="107"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="107"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="62"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="62"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="61"/>
+      <c r="N31" s="62"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="61"/>
+      <c r="Q31" s="62"/>
       <c r="R31" s="36"/>
       <c r="S31" s="36"/>
       <c r="T31" s="37"/>
@@ -10409,62 +10399,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10489,62 +10479,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/document/成果物ドキュメント_ログアウト機能.xlsx
+++ b/document/成果物ドキュメント_ログアウト機能.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-14\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER123\Desktop\作業中\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F3EAC3-D8DD-4E50-9160-A80EF358A001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5074C4DE-CC0C-4E58-8F34-0E61984E51E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,17 @@
     <sheet name="画面設計書" sheetId="5" r:id="rId5"/>
     <sheet name="テスト仕様書兼結果報告書" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="84">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
   <si>
     <t>初版</t>
-  </si>
-  <si>
-    <t>YYYY/MM/DD</t>
-  </si>
-  <si>
-    <t>チーム名</t>
   </si>
   <si>
     <t>ユースケース記述</t>
@@ -254,13 +248,6 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログアウト機能</t>
-    <rPh sb="5" eb="7">
-      <t>キノウ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>商品企画部の従業員(ユーザー)</t>
     <phoneticPr fontId="8"/>
   </si>
@@ -276,58 +263,6 @@
     <rPh sb="5" eb="7">
       <t>ガメン</t>
     </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.ユーザーがメニュー画面を開く
-2.ユーザーがログアウトボタンを押下する
-3.システムがログイン情報が削除される
-4.ログアウト画面画面が表示される
-5.ユーザーがログイン画面戻るボタンを押下する
-6.システムがログイン画面を表示する</t>
-    <rPh sb="11" eb="13">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>ヒラ</t>
-    </rPh>
-    <rPh sb="33" eb="35">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="49" eb="51">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="52" eb="54">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="65" eb="67">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="67" eb="69">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="70" eb="72">
-      <t>ヒョウジ</t>
-    </rPh>
-    <rPh sb="87" eb="89">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="89" eb="90">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="95" eb="97">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="111" eb="113">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>POST</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -350,36 +285,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログイン画面へ戻るボタンを表示する</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>モド</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>なし</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ログイン情報が削除されログイン画面が表示されること</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ヒョウジ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -387,11 +293,37 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログアウトされること</t>
+    <t>TaskManager62システム</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>TaskManager62システム</t>
+    <t>ログアウトする</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>チーム名 62期</t>
+    <rPh sb="7" eb="8">
+      <t>キ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1．ユーザーがメニュー画面でログアウトを選択する
+2．システムがログアウト画面を表示する
+3．ユーザーがログイン画面に戻る
+4．システムがログイン画面を表示する</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ユーザーがシステムからログアウトする</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>システムがユーザーの認証情報を消去し、ユーザーがシステムからログアウトすること</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>GET</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1175,7 +1107,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1227,12 +1159,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1293,6 +1219,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="57" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1341,15 +1294,9 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1377,9 +1324,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1416,21 +1360,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1447,9 +1376,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1521,23 +1447,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>34637</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>36829</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>235325</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>94687</xdr:rowOff>
+      <xdr:colOff>311728</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>24122</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
+        <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D195A1E-54BC-4F1F-EF5F-33147850916A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64A6F7E9-D024-10F3-EC8A-3E54AC15974B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1560,8 +1486,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1042148" y="1210235"/>
-          <a:ext cx="6891618" cy="4330511"/>
+          <a:off x="34637" y="2184284"/>
+          <a:ext cx="7966364" cy="1390065"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1587,23 +1513,89 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>298173</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>256761</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>285748</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>230759</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>430395</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>24847</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>775607</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>49432</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="図 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3597D64-77F4-3BF7-FD2C-916C45F3085A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7632AF9B-677D-6D2E-BFD3-0009C2F8463B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1306284" y="924723"/>
+          <a:ext cx="6068787" cy="4458709"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>840439</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>156883</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>1051917</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0D3C152B-3F09-9F1D-D699-4FCB2F77FA99}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1626,8 +1618,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="2857499" y="1548848"/>
-          <a:ext cx="3486679" cy="1871869"/>
+          <a:off x="3428998" y="1680883"/>
+          <a:ext cx="2430243" cy="1557617"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1856,85 +1848,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="82" t="s">
+      <c r="C2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
+      <c r="I2" s="43"/>
+      <c r="J2" s="43"/>
+      <c r="K2" s="43"/>
+      <c r="L2" s="43"/>
+      <c r="M2" s="43"/>
+      <c r="N2" s="43"/>
+      <c r="O2" s="43"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="41"/>
+      <c r="G3" s="41"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="41"/>
+      <c r="K3" s="41"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="41"/>
+      <c r="O3" s="41"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
-      <c r="I4" s="67"/>
-      <c r="J4" s="67"/>
-      <c r="K4" s="67"/>
-      <c r="L4" s="67"/>
-      <c r="M4" s="67"/>
-      <c r="N4" s="67"/>
-      <c r="O4" s="67"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
+      <c r="F4" s="41"/>
+      <c r="G4" s="41"/>
+      <c r="H4" s="41"/>
+      <c r="I4" s="41"/>
+      <c r="J4" s="41"/>
+      <c r="K4" s="41"/>
+      <c r="L4" s="41"/>
+      <c r="M4" s="41"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="67"/>
-      <c r="K5" s="67"/>
-      <c r="L5" s="67"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="41"/>
+      <c r="I5" s="41"/>
+      <c r="J5" s="41"/>
+      <c r="K5" s="41"/>
+      <c r="L5" s="41"/>
+      <c r="M5" s="41"/>
+      <c r="N5" s="41"/>
+      <c r="O5" s="41"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
-      <c r="G6" s="67"/>
-      <c r="H6" s="67"/>
-      <c r="I6" s="67"/>
-      <c r="J6" s="67"/>
-      <c r="K6" s="67"/>
-      <c r="L6" s="67"/>
-      <c r="M6" s="67"/>
-      <c r="N6" s="67"/>
-      <c r="O6" s="67"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="41"/>
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41"/>
+      <c r="N6" s="41"/>
+      <c r="O6" s="41"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -1954,46 +1946,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="84" t="s">
-        <v>85</v>
-      </c>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
+      <c r="E8" s="44" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="41"/>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="80" t="s">
+      <c r="G13" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="55"/>
-      <c r="I13" s="80" t="s">
-        <v>2</v>
-      </c>
-      <c r="J13" s="57"/>
-      <c r="K13" s="55"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="45">
+        <v>46128</v>
+      </c>
+      <c r="J13" s="38"/>
+      <c r="K13" s="39"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="80"/>
-      <c r="H14" s="55"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="55"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="38"/>
+      <c r="K14" s="39"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="80"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="57"/>
-      <c r="K15" s="55"/>
+      <c r="G15" s="37"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="39"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2002,13 +1994,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="81" t="s">
-        <v>3</v>
-      </c>
-      <c r="H17" s="67"/>
-      <c r="I17" s="67"/>
-      <c r="J17" s="67"/>
-      <c r="K17" s="67"/>
+      <c r="G17" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3022,216 +3014,216 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="39" t="s">
+      <c r="G1" s="47"/>
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="39" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="71"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="58"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="71"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="74" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="81" t="s">
+        <v>78</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="62" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="47">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="51"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="66"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="52"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="68"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="53"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="70" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="64"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="77" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="56" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="64"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="58" t="s">
-        <v>84</v>
-      </c>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="59"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="56" t="s">
+      <c r="B8" s="38"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="63" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="38"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="64"/>
+    </row>
+    <row r="9" spans="1:10" ht="91.5" customHeight="1">
+      <c r="A9" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="58" t="s">
-        <v>71</v>
-      </c>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="59"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="56" t="s">
+      <c r="B9" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="58" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="57"/>
-      <c r="F8" s="57"/>
-      <c r="G8" s="57"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="59"/>
-    </row>
-    <row r="9" spans="1:10" ht="91.5" customHeight="1">
-      <c r="A9" s="72" t="s">
+      <c r="C9" s="39"/>
+      <c r="D9" s="83" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="64"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="77"/>
+      <c r="B10" s="61" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="C10" s="39"/>
+      <c r="D10" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="38"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="64"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="78"/>
+      <c r="B11" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="55"/>
-      <c r="D9" s="79" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="57"/>
-      <c r="F9" s="57"/>
-      <c r="G9" s="57"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="59"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="73"/>
-      <c r="B10" s="54" t="s">
+      <c r="C11" s="39"/>
+      <c r="D11" s="63" t="s">
+        <v>75</v>
+      </c>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+      <c r="H11" s="38"/>
+      <c r="I11" s="38"/>
+      <c r="J11" s="64"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="55"/>
-      <c r="D10" s="58" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="57"/>
-      <c r="I10" s="57"/>
-      <c r="J10" s="59"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="74"/>
-      <c r="B11" s="54" t="s">
+      <c r="B12" s="38"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="64"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="55"/>
-      <c r="D11" s="58" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="57"/>
-      <c r="F11" s="57"/>
-      <c r="G11" s="57"/>
-      <c r="H11" s="57"/>
-      <c r="I11" s="57"/>
-      <c r="J11" s="59"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="56" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="58" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="57"/>
-      <c r="H12" s="57"/>
-      <c r="I12" s="57"/>
-      <c r="J12" s="59"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="61"/>
-      <c r="C13" s="62"/>
-      <c r="D13" s="75"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="61"/>
-      <c r="I13" s="61"/>
-      <c r="J13" s="76"/>
+      <c r="B13" s="66"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="79"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="66"/>
+      <c r="G13" s="66"/>
+      <c r="H13" s="66"/>
+      <c r="I13" s="66"/>
+      <c r="J13" s="80"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4267,72 +4259,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="39" t="s">
+      <c r="A1" s="84" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="47"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="39" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="41" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
+        <v>46120</v>
+      </c>
+      <c r="I2" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="47">
-        <v>46120</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>68</v>
-      </c>
-      <c r="J2" s="51"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="66"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="52"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="68"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -4642,7 +4634,7 @@
       <c r="G30" s="9"/>
       <c r="H30" s="9"/>
       <c r="I30" s="9"/>
-      <c r="K30" s="38"/>
+      <c r="K30" s="36"/>
     </row>
     <row r="31" spans="1:11" ht="12.75" customHeight="1">
       <c r="A31" s="8"/>
@@ -5687,72 +5679,72 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="39" t="s">
+      <c r="A1" s="84" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="47"/>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="39" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="41" t="s">
+      <c r="A2" s="71"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="47">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="51"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="66"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="52"/>
+      <c r="A3" s="71"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="68"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="49"/>
-      <c r="I4" s="49"/>
-      <c r="J4" s="53"/>
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="86"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="60"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5769,7 +5761,6 @@
     <row r="6" spans="1:10" ht="12.75" customHeight="1">
       <c r="A6" s="8"/>
       <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
       <c r="D6" s="9"/>
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
@@ -5939,7 +5930,6 @@
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
       <c r="D20" s="9"/>
-      <c r="E20" s="9"/>
       <c r="F20" s="9"/>
       <c r="G20" s="9"/>
       <c r="H20" s="9"/>
@@ -7085,6 +7075,7 @@
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7093,7 +7084,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J994"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -7103,339 +7094,271 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="85" t="s">
+      <c r="A1" s="84" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="47"/>
+      <c r="F1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="47"/>
+      <c r="H1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="71"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="49"/>
+      <c r="H2" s="54">
+        <v>46121</v>
+      </c>
+      <c r="I2" s="57" t="s">
+        <v>67</v>
+      </c>
+      <c r="J2" s="58"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="71"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="59"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="71"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="59"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="90" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="75"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="82"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="40"/>
-      <c r="F1" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="40"/>
-      <c r="H1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" s="42"/>
-      <c r="F2" s="41" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="64"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="91"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="92"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
+      <c r="G7" s="92"/>
+      <c r="H7" s="92"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="93"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="71"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="41"/>
+      <c r="G8" s="41"/>
+      <c r="H8" s="41"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="94"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="71"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="94"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="71"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="94"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="71"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="41"/>
+      <c r="I11" s="41"/>
+      <c r="J11" s="94"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="71"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="41"/>
+      <c r="H12" s="41"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="94"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="71"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="94"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="89" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="38"/>
+      <c r="D14" s="38"/>
+      <c r="E14" s="38"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="38"/>
+      <c r="H14" s="38"/>
+      <c r="I14" s="38"/>
+      <c r="J14" s="64"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="63" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="39"/>
+      <c r="I15" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="89" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="38"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="95" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="38"/>
+      <c r="J16" s="64"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A17" s="88" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="42"/>
-      <c r="H2" s="47">
-        <v>46121</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>69</v>
-      </c>
-      <c r="J2" s="51"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="66"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="44"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="52"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="66"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="43"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="43"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="48"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="52"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="88" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="92" t="s">
+      <c r="B17" s="66"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>73</v>
-      </c>
-      <c r="E5" s="71"/>
-      <c r="F5" s="71"/>
-      <c r="G5" s="71"/>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="78"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="90" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="59"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="93"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="95"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="66"/>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="96"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="66"/>
-      <c r="B9" s="67"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="67"/>
-      <c r="H9" s="67"/>
-      <c r="I9" s="67"/>
-      <c r="J9" s="96"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="66"/>
-      <c r="B10" s="67"/>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="67"/>
-      <c r="H10" s="67"/>
-      <c r="I10" s="67"/>
-      <c r="J10" s="96"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="66"/>
-      <c r="B11" s="67"/>
-      <c r="C11" s="67"/>
-      <c r="D11" s="67"/>
-      <c r="E11" s="67"/>
-      <c r="F11" s="67"/>
-      <c r="G11" s="67"/>
-      <c r="H11" s="67"/>
-      <c r="I11" s="67"/>
-      <c r="J11" s="96"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="66"/>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="96"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="66"/>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="67"/>
-      <c r="J13" s="96"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="90" t="s">
-        <v>25</v>
-      </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="57"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="59"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="90" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="57"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="58" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="90" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="55"/>
-      <c r="D16" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="97" t="s">
-        <v>19</v>
-      </c>
-      <c r="I16" s="57"/>
-      <c r="J16" s="59"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="91" t="s">
-        <v>77</v>
-      </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>78</v>
       </c>
       <c r="F17" s="18"/>
       <c r="G17" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="58" t="s">
-        <v>80</v>
-      </c>
-      <c r="I17" s="57"/>
-      <c r="J17" s="59"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="91"/>
-      <c r="B18" s="57"/>
-      <c r="C18" s="55"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="57"/>
-      <c r="J18" s="59"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="91"/>
-      <c r="B19" s="57"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="59"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="91"/>
-      <c r="B20" s="57"/>
-      <c r="C20" s="55"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="57"/>
-      <c r="J20" s="59"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="91"/>
-      <c r="B21" s="57"/>
-      <c r="C21" s="55"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="57"/>
-      <c r="J21" s="59"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="91"/>
-      <c r="B22" s="57"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="57"/>
-      <c r="J22" s="59"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="89"/>
-      <c r="B23" s="61"/>
-      <c r="C23" s="62"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="61"/>
-      <c r="J23" s="76"/>
-    </row>
+        <v>74</v>
+      </c>
+      <c r="H17" s="79"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="80"/>
+    </row>
+    <row r="18" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="19" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="20" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="21" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="22" spans="1:10" ht="12.75" customHeight="1"/>
+    <row r="23" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8407,30 +8330,13 @@
     <row r="992" ht="12.75" customHeight="1"/>
     <row r="993" ht="12.75" customHeight="1"/>
     <row r="994" ht="12.75" customHeight="1"/>
-    <row r="995" ht="12.75" customHeight="1"/>
-    <row r="996" ht="12.75" customHeight="1"/>
-    <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
+  <mergeCells count="19">
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A17:C17"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="A6:J6"/>
     <mergeCell ref="A7:J13"/>
@@ -8438,9 +8344,8 @@
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
     <mergeCell ref="H16:J16"/>
+    <mergeCell ref="D2:E4"/>
     <mergeCell ref="H17:J17"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H23:J23"/>
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
@@ -8465,182 +8370,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="68" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="69"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="69"/>
+      <c r="E1" s="69"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="46" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="47"/>
+      <c r="S1" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="T1" s="82"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="71"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="93"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="71"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="41"/>
+      <c r="I3" s="41"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="41"/>
+      <c r="M3" s="41"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="94"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="72"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="73"/>
+      <c r="M4" s="73"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="53"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="53"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="100"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="87" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
+      <c r="E5" s="75"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="81" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="39" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-      <c r="J1" s="40"/>
-      <c r="K1" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="40"/>
-      <c r="O1" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="40"/>
-      <c r="Q1" s="39" t="s">
-        <v>8</v>
-      </c>
-      <c r="R1" s="40"/>
-      <c r="S1" s="39" t="s">
-        <v>9</v>
-      </c>
-      <c r="T1" s="78"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="66"/>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="42"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="41"/>
-      <c r="T2" s="95"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="66"/>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
-      <c r="J3" s="44"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="67"/>
-      <c r="M3" s="67"/>
-      <c r="N3" s="44"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="44"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="44"/>
-      <c r="S3" s="43"/>
-      <c r="T3" s="96"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="68"/>
-      <c r="B4" s="69"/>
-      <c r="C4" s="69"/>
-      <c r="D4" s="69"/>
-      <c r="E4" s="69"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="69"/>
-      <c r="I4" s="69"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="69"/>
-      <c r="M4" s="69"/>
-      <c r="N4" s="46"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="46"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="46"/>
-      <c r="S4" s="45"/>
-      <c r="T4" s="102"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="88" t="s">
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="75"/>
+      <c r="K5" s="75"/>
+      <c r="L5" s="75"/>
+      <c r="M5" s="75"/>
+      <c r="N5" s="75"/>
+      <c r="O5" s="75"/>
+      <c r="P5" s="75"/>
+      <c r="Q5" s="75"/>
+      <c r="R5" s="75"/>
+      <c r="S5" s="75"/>
+      <c r="T5" s="82"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="71"/>
-      <c r="C5" s="71"/>
-      <c r="D5" s="71"/>
-      <c r="E5" s="71"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="77" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="64"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="89" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="71"/>
-      <c r="I5" s="71"/>
-      <c r="J5" s="71"/>
-      <c r="K5" s="71"/>
-      <c r="L5" s="71"/>
-      <c r="M5" s="71"/>
-      <c r="N5" s="71"/>
-      <c r="O5" s="71"/>
-      <c r="P5" s="71"/>
-      <c r="Q5" s="71"/>
-      <c r="R5" s="71"/>
-      <c r="S5" s="71"/>
-      <c r="T5" s="78"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="90" t="s">
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="63" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-      <c r="J6" s="57"/>
-      <c r="K6" s="57"/>
-      <c r="L6" s="57"/>
-      <c r="M6" s="57"/>
-      <c r="N6" s="57"/>
-      <c r="O6" s="57"/>
-      <c r="P6" s="57"/>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="57"/>
-      <c r="S6" s="57"/>
-      <c r="T6" s="59"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="90" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="58" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="57"/>
-      <c r="K7" s="57"/>
-      <c r="L7" s="57"/>
-      <c r="M7" s="57"/>
-      <c r="N7" s="57"/>
-      <c r="O7" s="57"/>
-      <c r="P7" s="57"/>
-      <c r="Q7" s="57"/>
-      <c r="R7" s="57"/>
-      <c r="S7" s="57"/>
-      <c r="T7" s="59"/>
+      <c r="H7" s="38"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="38"/>
+      <c r="K7" s="38"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="38"/>
+      <c r="P7" s="38"/>
+      <c r="Q7" s="38"/>
+      <c r="R7" s="38"/>
+      <c r="S7" s="38"/>
+      <c r="T7" s="64"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -8665,156 +8570,156 @@
       <c r="T8" s="10"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23" t="s">
+      <c r="A9" s="19"/>
+      <c r="B9" s="20"/>
+      <c r="C9" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="22"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="20"/>
+      <c r="Q9" s="20"/>
+      <c r="R9" s="20"/>
+      <c r="S9" s="20"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="20"/>
+      <c r="V9" s="20"/>
+      <c r="W9" s="20"/>
+      <c r="X9" s="20"/>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+    </row>
+    <row r="10" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A10" s="19"/>
+      <c r="B10" s="20"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24" t="s">
+      <c r="F10" s="20"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="26"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="P10" s="20"/>
+      <c r="Q10" s="20"/>
+      <c r="R10" s="20"/>
+      <c r="S10" s="20"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="20"/>
+      <c r="V10" s="20"/>
+      <c r="W10" s="20"/>
+      <c r="X10" s="20"/>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+    </row>
+    <row r="11" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A11" s="19"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
-    </row>
-    <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22" t="s">
+      <c r="F11" s="20"/>
+      <c r="G11" s="26"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="P11" s="20"/>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="20"/>
+      <c r="S11" s="20"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="20"/>
+      <c r="V11" s="20"/>
+      <c r="W11" s="20"/>
+      <c r="X11" s="20"/>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+    </row>
+    <row r="12" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A12" s="19"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
-    </row>
-    <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22" t="s">
+      <c r="F12" s="20"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
+      <c r="N12" s="20"/>
+      <c r="O12" s="20"/>
+      <c r="P12" s="20"/>
+      <c r="Q12" s="20"/>
+      <c r="R12" s="20"/>
+      <c r="S12" s="20"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="20"/>
+      <c r="V12" s="20"/>
+      <c r="W12" s="20"/>
+      <c r="X12" s="20"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+    </row>
+    <row r="13" spans="1:26" ht="12.75" customHeight="1">
+      <c r="A13" s="19"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
-    </row>
-    <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
-    </row>
-    <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="28"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="20"/>
+      <c r="M13" s="20"/>
+      <c r="N13" s="20"/>
+      <c r="O13" s="20"/>
+      <c r="P13" s="20"/>
+      <c r="Q13" s="20"/>
+      <c r="R13" s="20"/>
+      <c r="S13" s="20"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="20"/>
+      <c r="V13" s="20"/>
+      <c r="W13" s="20"/>
+      <c r="X13" s="20"/>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
     </row>
     <row r="14" spans="1:26" ht="8.25" customHeight="1">
       <c r="A14" s="8"/>
@@ -8839,522 +8744,522 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="90" t="s">
+      <c r="A15" s="89" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="39"/>
+      <c r="C15" s="103" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="39"/>
+      <c r="E15" s="95" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="39"/>
+      <c r="G15" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="D15" s="55"/>
-      <c r="E15" s="97" t="s">
+      <c r="H15" s="38"/>
+      <c r="I15" s="39"/>
+      <c r="J15" s="95" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="55"/>
-      <c r="G15" s="97" t="s">
+      <c r="K15" s="39"/>
+      <c r="L15" s="95" t="s">
         <v>47</v>
       </c>
-      <c r="H15" s="57"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="97" t="s">
+      <c r="M15" s="38"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="95" t="s">
         <v>48</v>
       </c>
-      <c r="K15" s="55"/>
-      <c r="L15" s="97" t="s">
+      <c r="P15" s="38"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="M15" s="57"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="97" t="s">
+      <c r="S15" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="P15" s="57"/>
-      <c r="Q15" s="55"/>
-      <c r="R15" s="15" t="s">
+      <c r="T15" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="S15" s="15" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="101">
+        <v>1</v>
+      </c>
+      <c r="B16" s="39"/>
+      <c r="C16" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="T15" s="32" t="s">
+      <c r="D16" s="39"/>
+      <c r="E16" s="102" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="103">
-        <v>1</v>
-      </c>
-      <c r="B16" s="55"/>
-      <c r="C16" s="104" t="s">
+      <c r="F16" s="39"/>
+      <c r="G16" s="96" t="s">
         <v>54</v>
       </c>
-      <c r="D16" s="55"/>
-      <c r="E16" s="104" t="s">
+      <c r="H16" s="38"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="96" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="55"/>
-      <c r="G16" s="98" t="s">
+      <c r="K16" s="39"/>
+      <c r="L16" s="98" t="s">
         <v>56</v>
       </c>
-      <c r="H16" s="57"/>
-      <c r="I16" s="55"/>
-      <c r="J16" s="98" t="s">
+      <c r="M16" s="38"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="55"/>
-      <c r="L16" s="100" t="s">
+      <c r="P16" s="38"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="31"/>
+      <c r="T16" s="32"/>
+      <c r="U16" s="33"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="33"/>
+      <c r="Y16" s="33"/>
+      <c r="Z16" s="33"/>
+    </row>
+    <row r="17" spans="1:26" ht="41.25" customHeight="1">
+      <c r="A17" s="101">
+        <v>2</v>
+      </c>
+      <c r="B17" s="39"/>
+      <c r="C17" s="102" t="s">
         <v>58</v>
       </c>
-      <c r="M16" s="57"/>
-      <c r="N16" s="55"/>
-      <c r="O16" s="100" t="s">
+      <c r="D17" s="39"/>
+      <c r="E17" s="102" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="57"/>
-      <c r="Q16" s="55"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
-    </row>
-    <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="103">
-        <v>2</v>
-      </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="104" t="s">
+      <c r="F17" s="39"/>
+      <c r="G17" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="D17" s="55"/>
-      <c r="E17" s="104" t="s">
+      <c r="H17" s="38"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="55"/>
-      <c r="G17" s="98" t="s">
+      <c r="K17" s="39"/>
+      <c r="L17" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="57"/>
-      <c r="I17" s="55"/>
-      <c r="J17" s="98" t="s">
+      <c r="M17" s="38"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="55"/>
-      <c r="L17" s="100" t="s">
-        <v>64</v>
-      </c>
-      <c r="M17" s="57"/>
-      <c r="N17" s="55"/>
-      <c r="O17" s="100" t="s">
-        <v>65</v>
-      </c>
-      <c r="P17" s="57"/>
-      <c r="Q17" s="55"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
+      <c r="P17" s="38"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="33"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="33"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="103"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="55"/>
-      <c r="G18" s="98"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="55"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="55"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="57"/>
-      <c r="N18" s="55"/>
-      <c r="O18" s="100"/>
-      <c r="P18" s="57"/>
-      <c r="Q18" s="55"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
+      <c r="A18" s="101"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="102"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="102"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="96"/>
+      <c r="K18" s="39"/>
+      <c r="L18" s="98"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="98"/>
+      <c r="P18" s="38"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="31"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="33"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="33"/>
+      <c r="Y18" s="33"/>
+      <c r="Z18" s="33"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="103"/>
-      <c r="B19" s="55"/>
-      <c r="C19" s="104"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="104"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="98"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="57"/>
-      <c r="N19" s="55"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="57"/>
-      <c r="Q19" s="55"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
+      <c r="A19" s="101"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="102"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="102"/>
+      <c r="F19" s="39"/>
+      <c r="G19" s="96"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="39"/>
+      <c r="J19" s="96"/>
+      <c r="K19" s="39"/>
+      <c r="L19" s="98"/>
+      <c r="M19" s="38"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="98"/>
+      <c r="P19" s="38"/>
+      <c r="Q19" s="39"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="31"/>
+      <c r="T19" s="32"/>
+      <c r="U19" s="33"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="33"/>
+      <c r="Y19" s="33"/>
+      <c r="Z19" s="33"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="103"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="104"/>
-      <c r="D20" s="55"/>
-      <c r="E20" s="104"/>
-      <c r="F20" s="55"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="55"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="55"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="57"/>
-      <c r="N20" s="55"/>
-      <c r="O20" s="100"/>
-      <c r="P20" s="57"/>
-      <c r="Q20" s="55"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
+      <c r="A20" s="101"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="39"/>
+      <c r="G20" s="96"/>
+      <c r="H20" s="38"/>
+      <c r="I20" s="39"/>
+      <c r="J20" s="96"/>
+      <c r="K20" s="39"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="38"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="98"/>
+      <c r="P20" s="38"/>
+      <c r="Q20" s="39"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="33"/>
+      <c r="V20" s="33"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="33"/>
+      <c r="Y20" s="33"/>
+      <c r="Z20" s="33"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="103"/>
-      <c r="B21" s="55"/>
-      <c r="C21" s="104"/>
-      <c r="D21" s="55"/>
-      <c r="E21" s="104"/>
-      <c r="F21" s="55"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="57"/>
-      <c r="I21" s="55"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="55"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="57"/>
-      <c r="N21" s="55"/>
-      <c r="O21" s="100"/>
-      <c r="P21" s="57"/>
-      <c r="Q21" s="55"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
+      <c r="A21" s="101"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="102"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="102"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="38"/>
+      <c r="I21" s="39"/>
+      <c r="J21" s="96"/>
+      <c r="K21" s="39"/>
+      <c r="L21" s="98"/>
+      <c r="M21" s="38"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="98"/>
+      <c r="P21" s="38"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="31"/>
+      <c r="T21" s="32"/>
+      <c r="U21" s="33"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="33"/>
+      <c r="Y21" s="33"/>
+      <c r="Z21" s="33"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="103"/>
-      <c r="B22" s="55"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="104"/>
-      <c r="F22" s="55"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="57"/>
-      <c r="I22" s="55"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="55"/>
-      <c r="L22" s="100"/>
-      <c r="M22" s="57"/>
-      <c r="N22" s="55"/>
-      <c r="O22" s="100"/>
-      <c r="P22" s="57"/>
-      <c r="Q22" s="55"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
+      <c r="A22" s="101"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="102"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="102"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="96"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="96"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="98"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="98"/>
+      <c r="P22" s="38"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="31"/>
+      <c r="T22" s="32"/>
+      <c r="U22" s="33"/>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="33"/>
+      <c r="Y22" s="33"/>
+      <c r="Z22" s="33"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="103"/>
-      <c r="B23" s="55"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="55"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="57"/>
-      <c r="I23" s="55"/>
-      <c r="J23" s="98"/>
-      <c r="K23" s="55"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="57"/>
-      <c r="N23" s="55"/>
-      <c r="O23" s="100"/>
-      <c r="P23" s="57"/>
-      <c r="Q23" s="55"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
+      <c r="A23" s="101"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="102"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="102"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="96"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="96"/>
+      <c r="K23" s="39"/>
+      <c r="L23" s="98"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="98"/>
+      <c r="P23" s="38"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="32"/>
+      <c r="U23" s="33"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="33"/>
+      <c r="Y23" s="33"/>
+      <c r="Z23" s="33"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="103"/>
-      <c r="B24" s="55"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="104"/>
-      <c r="F24" s="55"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="57"/>
-      <c r="I24" s="55"/>
-      <c r="J24" s="98"/>
-      <c r="K24" s="55"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="57"/>
-      <c r="N24" s="55"/>
-      <c r="O24" s="100"/>
-      <c r="P24" s="57"/>
-      <c r="Q24" s="55"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
+      <c r="A24" s="101"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="102"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="102"/>
+      <c r="F24" s="39"/>
+      <c r="G24" s="96"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="39"/>
+      <c r="J24" s="96"/>
+      <c r="K24" s="39"/>
+      <c r="L24" s="98"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="98"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="39"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="31"/>
+      <c r="T24" s="32"/>
+      <c r="U24" s="33"/>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="33"/>
+      <c r="Y24" s="33"/>
+      <c r="Z24" s="33"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="103"/>
-      <c r="B25" s="55"/>
-      <c r="C25" s="104"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="104"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="57"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="55"/>
-      <c r="L25" s="100"/>
-      <c r="M25" s="57"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="57"/>
-      <c r="Q25" s="55"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
+      <c r="A25" s="101"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="96"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="96"/>
+      <c r="K25" s="39"/>
+      <c r="L25" s="98"/>
+      <c r="M25" s="38"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="98"/>
+      <c r="P25" s="38"/>
+      <c r="Q25" s="39"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="32"/>
+      <c r="U25" s="33"/>
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="33"/>
+      <c r="Y25" s="33"/>
+      <c r="Z25" s="33"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="103"/>
-      <c r="B26" s="55"/>
-      <c r="C26" s="104"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="104"/>
-      <c r="F26" s="55"/>
-      <c r="G26" s="98"/>
-      <c r="H26" s="57"/>
-      <c r="I26" s="55"/>
-      <c r="J26" s="98"/>
-      <c r="K26" s="55"/>
-      <c r="L26" s="100"/>
-      <c r="M26" s="57"/>
-      <c r="N26" s="55"/>
-      <c r="O26" s="100"/>
-      <c r="P26" s="57"/>
-      <c r="Q26" s="55"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
+      <c r="A26" s="101"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="102"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="102"/>
+      <c r="F26" s="39"/>
+      <c r="G26" s="96"/>
+      <c r="H26" s="38"/>
+      <c r="I26" s="39"/>
+      <c r="J26" s="96"/>
+      <c r="K26" s="39"/>
+      <c r="L26" s="98"/>
+      <c r="M26" s="38"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="98"/>
+      <c r="P26" s="38"/>
+      <c r="Q26" s="39"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="32"/>
+      <c r="U26" s="33"/>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="33"/>
+      <c r="Y26" s="33"/>
+      <c r="Z26" s="33"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="103"/>
-      <c r="B27" s="55"/>
-      <c r="C27" s="104"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="104"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="98"/>
-      <c r="H27" s="57"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="98"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="57"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="100"/>
-      <c r="P27" s="57"/>
-      <c r="Q27" s="55"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
+      <c r="A27" s="101"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="102"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="102"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="96"/>
+      <c r="H27" s="38"/>
+      <c r="I27" s="39"/>
+      <c r="J27" s="96"/>
+      <c r="K27" s="39"/>
+      <c r="L27" s="98"/>
+      <c r="M27" s="38"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="98"/>
+      <c r="P27" s="38"/>
+      <c r="Q27" s="39"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="31"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="103"/>
-      <c r="B28" s="55"/>
-      <c r="C28" s="104"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="55"/>
-      <c r="G28" s="98"/>
-      <c r="H28" s="57"/>
-      <c r="I28" s="55"/>
-      <c r="J28" s="98"/>
-      <c r="K28" s="55"/>
-      <c r="L28" s="100"/>
-      <c r="M28" s="57"/>
-      <c r="N28" s="55"/>
-      <c r="O28" s="100"/>
-      <c r="P28" s="57"/>
-      <c r="Q28" s="55"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
+      <c r="A28" s="101"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="102"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="102"/>
+      <c r="F28" s="39"/>
+      <c r="G28" s="96"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="39"/>
+      <c r="L28" s="98"/>
+      <c r="M28" s="38"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="98"/>
+      <c r="P28" s="38"/>
+      <c r="Q28" s="39"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="33"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="33"/>
+      <c r="Y28" s="33"/>
+      <c r="Z28" s="33"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="103"/>
-      <c r="B29" s="55"/>
-      <c r="C29" s="104"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="104"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="98"/>
-      <c r="H29" s="57"/>
-      <c r="I29" s="55"/>
-      <c r="J29" s="98"/>
-      <c r="K29" s="55"/>
-      <c r="L29" s="100"/>
-      <c r="M29" s="57"/>
-      <c r="N29" s="55"/>
-      <c r="O29" s="100"/>
-      <c r="P29" s="57"/>
-      <c r="Q29" s="55"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
+      <c r="A29" s="101"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="102"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="102"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="96"/>
+      <c r="H29" s="38"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="96"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="98"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="98"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="33"/>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="33"/>
+      <c r="Y29" s="33"/>
+      <c r="Z29" s="33"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="103"/>
-      <c r="B30" s="55"/>
-      <c r="C30" s="104"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="104"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="98"/>
-      <c r="H30" s="57"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="98"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="57"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="57"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
+      <c r="A30" s="101"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="102"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="102"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="96"/>
+      <c r="H30" s="38"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="96"/>
+      <c r="K30" s="39"/>
+      <c r="L30" s="98"/>
+      <c r="M30" s="38"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="98"/>
+      <c r="P30" s="38"/>
+      <c r="Q30" s="39"/>
+      <c r="R30" s="31"/>
+      <c r="S30" s="31"/>
+      <c r="T30" s="32"/>
+      <c r="U30" s="33"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="33"/>
+      <c r="Y30" s="33"/>
+      <c r="Z30" s="33"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="106"/>
-      <c r="B31" s="62"/>
-      <c r="C31" s="107"/>
-      <c r="D31" s="62"/>
-      <c r="E31" s="107"/>
-      <c r="F31" s="62"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="62"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="62"/>
-      <c r="L31" s="101"/>
-      <c r="M31" s="61"/>
-      <c r="N31" s="62"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="61"/>
-      <c r="Q31" s="62"/>
-      <c r="R31" s="36"/>
-      <c r="S31" s="36"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
+      <c r="A31" s="104"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="97"/>
+      <c r="H31" s="66"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="97"/>
+      <c r="K31" s="67"/>
+      <c r="L31" s="99"/>
+      <c r="M31" s="66"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="99"/>
+      <c r="P31" s="66"/>
+      <c r="Q31" s="67"/>
+      <c r="R31" s="34"/>
+      <c r="S31" s="34"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="33"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="33"/>
+      <c r="Y31" s="33"/>
+      <c r="Z31" s="33"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
       <c r="D32" s="3"/>
